--- a/test/res/task.xlsx
+++ b/test/res/task.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/codetypes/Desktop/Github/xlsx-exporter/test/res/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{68186292-A074-B04B-A2B6-FC43F57D1FF2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CE6C439-CCEA-C948-96A3-D801C1C5A393}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17700" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1101,7 +1101,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="262">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="263">
   <si>
     <t>id</t>
   </si>
@@ -1886,16 +1886,19 @@
     <t>$ &gt; 0 &amp;&amp; $ &lt; 20</t>
   </si>
   <si>
-    <t>#main.type=$&amp;key2=MAIN&amp;#main.condition=mainline_event</t>
-  </si>
-  <si>
-    <t>item#item.id=$.id</t>
-  </si>
-  <si>
-    <t>item#*.id=$.id</t>
-  </si>
-  <si>
-    <t>#define.value=$&amp;#define.key1=TASK_TYPE</t>
+    <t>#define.value&amp;key1=TASK_TYPE</t>
+  </si>
+  <si>
+    <t>$&amp;key2=MAIN==#main.type&amp;condition=mainline_event</t>
+  </si>
+  <si>
+    <t>$[*].id==item#item.id</t>
+  </si>
+  <si>
+    <t>$[*].id==item#*.id</t>
+  </si>
+  <si>
+    <t>$[*]==#branch.id</t>
   </si>
 </sst>
 </file>
@@ -3277,7 +3280,7 @@
         <v>13</v>
       </c>
       <c r="F5" s="33" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="G5" s="33" t="s">
         <v>13</v>
@@ -4159,7 +4162,7 @@
         <v>257</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>13</v>
@@ -4168,7 +4171,7 @@
         <v>101</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>102</v>
+        <v>262</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>13</v>
@@ -6538,10 +6541,10 @@
         <v>13</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="I4" s="2" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="J4" s="2" t="s">
         <v>13</v>

--- a/test/res/task.xlsx
+++ b/test/res/task.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/codetypes/Desktop/Github/xlsx-exporter/test/res/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\bite\Desktop\github\xlsx-exporter\test\res\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5CE6C439-CCEA-C948-96A3-D801C1C5A393}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{680E7CDA-1B5E-4422-9861-44EDCE174D05}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="17700" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-37740" yWindow="435" windowWidth="33675" windowHeight="19725" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="define" sheetId="9" r:id="rId1"/>
@@ -1101,7 +1101,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="263">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="264">
   <si>
     <t>id</t>
   </si>
@@ -1383,9 +1383,6 @@
   </si>
   <si>
     <t>need_lv</t>
-  </si>
-  <si>
-    <t>task_type</t>
   </si>
   <si>
     <t>int?</t>
@@ -1899,17 +1896,25 @@
   </si>
   <si>
     <t>$[*]==#branch.id</t>
+  </si>
+  <si>
+    <t>TaskType</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>$[*].id==item#item.id</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1938,7 +1943,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1958,7 +1963,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="Calibri"/>
+      <name val="等线"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -2244,7 +2249,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="常规" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
     <cellStyle name="常规 3" xfId="2" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
   </cellStyles>
@@ -3170,19 +3175,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I24"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="14.6640625" customWidth="1"/>
-    <col min="3" max="3" width="16.6640625" customWidth="1"/>
-    <col min="4" max="4" width="25.6640625" customWidth="1"/>
-    <col min="5" max="5" width="45.83203125" customWidth="1"/>
-    <col min="6" max="6" width="18.6640625" customWidth="1"/>
-    <col min="8" max="9" width="12.6640625" customWidth="1"/>
+    <col min="2" max="2" width="14.625" customWidth="1"/>
+    <col min="3" max="3" width="16.625" customWidth="1"/>
+    <col min="4" max="4" width="25.625" customWidth="1"/>
+    <col min="5" max="5" width="45.875" customWidth="1"/>
+    <col min="6" max="6" width="18.625" customWidth="1"/>
+    <col min="8" max="9" width="12.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="42" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B1" s="43"/>
       <c r="C1" s="43"/>
@@ -3190,7 +3195,7 @@
       <c r="E1" s="43"/>
       <c r="F1" s="43"/>
     </row>
-    <row r="2" spans="1:9" ht="16">
+    <row r="2" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -3216,10 +3221,10 @@
         <v>7</v>
       </c>
       <c r="I2" s="34" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="16">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -3245,15 +3250,15 @@
         <v>10</v>
       </c>
       <c r="I3" s="34" t="s">
-        <v>248</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" ht="16">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
       <c r="B4" s="33" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="C4" s="33"/>
       <c r="D4" s="33"/>
@@ -3263,7 +3268,7 @@
       <c r="H4" s="34"/>
       <c r="I4" s="34"/>
     </row>
-    <row r="5" spans="1:9" ht="16">
+    <row r="5" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -3280,7 +3285,7 @@
         <v>13</v>
       </c>
       <c r="F5" s="33" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G5" s="33" t="s">
         <v>13</v>
@@ -3292,7 +3297,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="16">
+    <row r="6" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -3309,7 +3314,7 @@
       <c r="H6" s="34"/>
       <c r="I6" s="34"/>
     </row>
-    <row r="7" spans="1:9" ht="16">
+    <row r="7" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A7" s="21" t="s">
         <v>17</v>
       </c>
@@ -3335,10 +3340,10 @@
         <v>23</v>
       </c>
       <c r="I7" s="35" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="16">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A8" s="21" t="s">
         <v>17</v>
       </c>
@@ -3361,7 +3366,7 @@
       <c r="H8" s="35"/>
       <c r="I8" s="35"/>
     </row>
-    <row r="9" spans="1:9" ht="16">
+    <row r="9" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A9" s="21" t="s">
         <v>17</v>
       </c>
@@ -3384,7 +3389,7 @@
       <c r="H9" s="35"/>
       <c r="I9" s="35"/>
     </row>
-    <row r="10" spans="1:9" ht="16">
+    <row r="10" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A10" s="21" t="s">
         <v>17</v>
       </c>
@@ -3407,7 +3412,7 @@
       <c r="H10" s="35"/>
       <c r="I10" s="35"/>
     </row>
-    <row r="11" spans="1:9" ht="16">
+    <row r="11" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A11" s="21" t="s">
         <v>17</v>
       </c>
@@ -3430,7 +3435,7 @@
       <c r="H11" s="35"/>
       <c r="I11" s="35"/>
     </row>
-    <row r="12" spans="1:9" ht="16">
+    <row r="12" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A12" s="21" t="s">
         <v>17</v>
       </c>
@@ -3453,7 +3458,7 @@
       <c r="H12" s="35"/>
       <c r="I12" s="35"/>
     </row>
-    <row r="13" spans="1:9" ht="16">
+    <row r="13" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A13" s="21" t="s">
         <v>17</v>
       </c>
@@ -3476,7 +3481,7 @@
       <c r="H13" s="35"/>
       <c r="I13" s="35"/>
     </row>
-    <row r="14" spans="1:9" ht="16">
+    <row r="14" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A14" s="21" t="s">
         <v>17</v>
       </c>
@@ -3503,7 +3508,7 @@
       </c>
       <c r="I14" s="35"/>
     </row>
-    <row r="15" spans="1:9" ht="16">
+    <row r="15" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A15" s="21" t="s">
         <v>17</v>
       </c>
@@ -3526,7 +3531,7 @@
       <c r="H15" s="35"/>
       <c r="I15" s="35"/>
     </row>
-    <row r="16" spans="1:9" ht="16">
+    <row r="16" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A16" s="21" t="s">
         <v>17</v>
       </c>
@@ -3549,7 +3554,7 @@
       <c r="H16" s="35"/>
       <c r="I16" s="35"/>
     </row>
-    <row r="17" spans="1:9" ht="16">
+    <row r="17" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A17" s="21" t="s">
         <v>17</v>
       </c>
@@ -3572,7 +3577,7 @@
       <c r="H17" s="35"/>
       <c r="I17" s="35"/>
     </row>
-    <row r="18" spans="1:9" ht="16">
+    <row r="18" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A18" s="21" t="s">
         <v>17</v>
       </c>
@@ -3595,7 +3600,7 @@
       <c r="H18" s="35"/>
       <c r="I18" s="35"/>
     </row>
-    <row r="19" spans="1:9" ht="16">
+    <row r="19" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A19" s="21" t="s">
         <v>17</v>
       </c>
@@ -3618,7 +3623,7 @@
       <c r="H19" s="35"/>
       <c r="I19" s="35"/>
     </row>
-    <row r="20" spans="1:9" ht="16">
+    <row r="20" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A20" s="21" t="s">
         <v>17</v>
       </c>
@@ -3645,7 +3650,7 @@
       </c>
       <c r="I20" s="35"/>
     </row>
-    <row r="21" spans="1:9" ht="16">
+    <row r="21" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A21" s="21" t="s">
         <v>17</v>
       </c>
@@ -3668,7 +3673,7 @@
       <c r="H21" s="35"/>
       <c r="I21" s="35"/>
     </row>
-    <row r="22" spans="1:9" ht="16">
+    <row r="22" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A22" s="21" t="s">
         <v>17</v>
       </c>
@@ -3691,7 +3696,7 @@
       <c r="H22" s="35"/>
       <c r="I22" s="35"/>
     </row>
-    <row r="23" spans="1:9" ht="16">
+    <row r="23" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A23" s="21" t="s">
         <v>17</v>
       </c>
@@ -3714,7 +3719,7 @@
       <c r="H23" s="35"/>
       <c r="I23" s="35"/>
     </row>
-    <row r="24" spans="1:9" ht="16">
+    <row r="24" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
       <c r="A24" s="21" t="s">
         <v>17</v>
       </c>
@@ -3750,30 +3755,30 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{984B885C-48D0-4D9B-AAB3-39C5F463E278}">
   <dimension ref="A1:E10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="41"/>
     <col min="2" max="2" width="32.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="49" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A1" s="44" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="B1" s="45"/>
       <c r="C1" s="45"/>
       <c r="D1" s="45"/>
       <c r="E1" s="45"/>
     </row>
-    <row r="2" spans="1:5" ht="16">
+    <row r="2" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>5</v>
@@ -3785,7 +3790,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="16">
+    <row r="3" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -3802,7 +3807,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="16">
+    <row r="4" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
@@ -3811,7 +3816,7 @@
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
     </row>
-    <row r="5" spans="1:5" ht="16">
+    <row r="5" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -3828,29 +3833,29 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="16">
+    <row r="6" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B6" s="38" t="s">
+        <v>235</v>
+      </c>
+      <c r="C6" s="38" t="s">
         <v>236</v>
       </c>
-      <c r="C6" s="38" t="s">
+      <c r="D6" s="38" t="s">
         <v>237</v>
       </c>
-      <c r="D6" s="38" t="s">
-        <v>238</v>
-      </c>
       <c r="E6" s="38" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A7" s="41" t="s">
         <v>17</v>
       </c>
       <c r="B7" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="C7" s="39">
         <v>1200</v>
@@ -3859,15 +3864,15 @@
         <v>22</v>
       </c>
       <c r="E7" s="40" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A8" s="41" t="s">
         <v>17</v>
       </c>
       <c r="B8" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="C8" s="39">
         <v>3</v>
@@ -3876,15 +3881,15 @@
         <v>22</v>
       </c>
       <c r="E8" t="s">
-        <v>242</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A9" s="41" t="s">
         <v>17</v>
       </c>
       <c r="B9" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="C9" s="39">
         <f>7*3600</f>
@@ -3894,15 +3899,15 @@
         <v>22</v>
       </c>
       <c r="E9" t="s">
-        <v>244</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A10" s="41" t="s">
         <v>17</v>
       </c>
       <c r="B10" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="C10" s="39">
         <f>0.5*3600</f>
@@ -3912,7 +3917,7 @@
         <v>22</v>
       </c>
       <c r="E10" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
   </sheetData>
@@ -3928,26 +3933,26 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:X17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17.1640625" style="9" customWidth="1"/>
-    <col min="2" max="2" width="17.83203125" style="9" customWidth="1"/>
-    <col min="3" max="4" width="15.1640625" style="9" customWidth="1"/>
-    <col min="5" max="5" width="26.83203125" style="9" customWidth="1"/>
-    <col min="6" max="6" width="8.6640625" style="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.1640625" style="8" customWidth="1"/>
-    <col min="8" max="8" width="23.1640625" style="9" customWidth="1"/>
+    <col min="1" max="1" width="17.125" style="9" customWidth="1"/>
+    <col min="2" max="2" width="17.875" style="9" customWidth="1"/>
+    <col min="3" max="4" width="15.125" style="9" customWidth="1"/>
+    <col min="5" max="5" width="26.875" style="9" customWidth="1"/>
+    <col min="6" max="6" width="8.625" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.125" style="8" customWidth="1"/>
+    <col min="8" max="8" width="23.125" style="9" customWidth="1"/>
     <col min="9" max="9" width="5" style="9" customWidth="1"/>
-    <col min="10" max="10" width="46.1640625" style="9" customWidth="1"/>
+    <col min="10" max="10" width="46.125" style="9" customWidth="1"/>
     <col min="11" max="11" width="31.5" style="9" customWidth="1"/>
     <col min="12" max="12" width="8" style="9" customWidth="1"/>
-    <col min="13" max="13" width="73.6640625" style="9" customWidth="1"/>
-    <col min="14" max="14" width="13.1640625" style="9" customWidth="1"/>
-    <col min="15" max="15" width="20.6640625" style="8" customWidth="1"/>
+    <col min="13" max="13" width="73.625" style="9" customWidth="1"/>
+    <col min="14" max="14" width="13.125" style="9" customWidth="1"/>
+    <col min="15" max="15" width="20.625" style="8" customWidth="1"/>
     <col min="16" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -4021,7 +4026,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="2" spans="1:24">
+    <row r="2" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A2" s="21" t="s">
         <v>22</v>
       </c>
@@ -4032,37 +4037,37 @@
         <v>22</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>94</v>
+        <v>262</v>
       </c>
       <c r="E2" s="2" t="s">
         <v>11</v>
       </c>
       <c r="F2" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="G2" s="22" t="s">
         <v>95</v>
-      </c>
-      <c r="G2" s="22" t="s">
-        <v>96</v>
       </c>
       <c r="H2" s="2" t="s">
         <v>11</v>
       </c>
       <c r="I2" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="J2" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>98</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>99</v>
       </c>
       <c r="L2" s="2" t="s">
         <v>11</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O2" s="1" t="s">
         <v>11</v>
@@ -4095,7 +4100,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:24">
+    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A3" s="21" t="s">
         <v>12</v>
       </c>
@@ -4112,13 +4117,13 @@
       <c r="J3" s="2"/>
       <c r="K3" s="2"/>
       <c r="L3" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="O3" s="1" t="s">
         <v>13</v>
@@ -4151,7 +4156,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:24">
+    <row r="4" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A4" s="21" t="s">
         <v>14</v>
       </c>
@@ -4159,19 +4164,19 @@
         <v>13</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>256</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>257</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>258</v>
-      </c>
       <c r="E4" s="2" t="s">
         <v>13</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H4" s="2" t="s">
         <v>13</v>
@@ -4180,11 +4185,11 @@
         <v>13</v>
       </c>
       <c r="J4" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="K4" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="K4" s="2" t="s">
-        <v>104</v>
-      </c>
       <c r="L4" s="2" t="s">
         <v>13</v>
       </c>
@@ -4192,7 +4197,7 @@
         <v>13</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="O4" s="12" t="s">
         <v>13</v>
@@ -4225,84 +4230,84 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:24">
+    <row r="5" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A5" s="21" t="s">
         <v>15</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C5" s="7" t="s">
         <v>105</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>106</v>
       </c>
       <c r="D5" s="7" t="s">
         <v>18</v>
       </c>
       <c r="E5" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="F5" s="7" t="s">
         <v>107</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>108</v>
       </c>
       <c r="G5" s="23" t="s">
         <v>25</v>
       </c>
       <c r="H5" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="I5" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="J5" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="J5" s="13" t="s">
+      <c r="K5" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="K5" s="13" t="s">
+      <c r="L5" s="13" t="s">
         <v>112</v>
-      </c>
-      <c r="L5" s="13" t="s">
-        <v>113</v>
       </c>
       <c r="M5" s="13"/>
       <c r="N5" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="O5" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="O5" s="9" t="s">
+      <c r="P5" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="P5" s="9" t="s">
+      <c r="Q5" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="Q5" s="9" t="s">
+      <c r="R5" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="R5" s="9" t="s">
+      <c r="S5" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="T5" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="S5" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="T5" s="9" t="s">
+      <c r="U5" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="V5" s="9" t="s">
         <v>119</v>
       </c>
-      <c r="U5" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="V5" s="9" t="s">
+      <c r="W5" s="9" t="s">
         <v>120</v>
       </c>
-      <c r="W5" s="9" t="s">
+      <c r="X5" s="9" t="s">
         <v>121</v>
       </c>
-      <c r="X5" s="9" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="6" spans="1:24" ht="17">
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A6" s="24">
         <v>1001</v>
       </c>
       <c r="B6" s="25" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C6" s="15">
         <v>1</v>
@@ -4311,7 +4316,7 @@
         <v>20</v>
       </c>
       <c r="E6" s="25" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F6" s="15">
         <f t="shared" ref="F6:F16" si="0">A7</f>
@@ -4325,7 +4330,7 @@
         <v>1</v>
       </c>
       <c r="J6" s="19" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="K6" s="15" t="str">
         <f>"{"&amp;O6&amp;"}"</f>
@@ -4335,7 +4340,7 @@
         <v>0</v>
       </c>
       <c r="M6" s="29" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="N6" s="9">
         <v>1</v>
@@ -4362,12 +4367,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24">
+    <row r="7" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A7" s="24">
         <v>1002</v>
       </c>
       <c r="B7" s="25" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C7" s="15">
         <v>2</v>
@@ -4376,7 +4381,7 @@
         <v>20</v>
       </c>
       <c r="E7" s="25" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="F7" s="15">
         <f t="shared" si="0"/>
@@ -4390,7 +4395,7 @@
         <v>1</v>
       </c>
       <c r="J7" s="8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="K7" s="15" t="str">
         <f t="shared" ref="K7:K9" si="1">"{"&amp;O7&amp;"}"</f>
@@ -4422,12 +4427,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:24" ht="17">
+    <row r="8" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A8" s="24">
         <v>1003</v>
       </c>
       <c r="B8" s="25" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="C8" s="15">
         <v>3</v>
@@ -4436,7 +4441,7 @@
         <v>20</v>
       </c>
       <c r="E8" s="25" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="F8" s="15">
         <f t="shared" si="0"/>
@@ -4449,7 +4454,7 @@
         <v>1</v>
       </c>
       <c r="J8" s="19" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="K8" s="15" t="str">
         <f t="shared" si="1"/>
@@ -4487,12 +4492,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:24" ht="17">
+    <row r="9" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A9" s="24">
         <v>1014</v>
       </c>
       <c r="B9" s="25" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C9" s="15">
         <v>4</v>
@@ -4501,14 +4506,14 @@
         <v>20</v>
       </c>
       <c r="E9" s="25" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="F9" s="15">
         <f t="shared" si="0"/>
         <v>100301</v>
       </c>
       <c r="G9" s="19" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H9" s="16" t="s">
         <v>57</v>
@@ -4549,12 +4554,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:24">
+    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A10" s="24">
         <v>100301</v>
       </c>
       <c r="B10" s="25" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C10" s="15">
         <v>5</v>
@@ -4563,14 +4568,14 @@
         <v>20</v>
       </c>
       <c r="E10" s="25" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="F10" s="15">
         <f t="shared" si="0"/>
         <v>100302</v>
       </c>
       <c r="G10" s="19" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H10" s="9" t="s">
         <v>38</v>
@@ -4579,7 +4584,7 @@
         <v>1</v>
       </c>
       <c r="J10" s="8" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="K10" s="15" t="str">
         <f t="shared" ref="K10:K11" si="3">"{"&amp;O10&amp;"}"</f>
@@ -4589,7 +4594,7 @@
         <v>0</v>
       </c>
       <c r="M10" s="29" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="N10" s="9">
         <v>1</v>
@@ -4619,12 +4624,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:24" ht="17">
+    <row r="11" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A11" s="24">
         <v>100302</v>
       </c>
       <c r="B11" s="25" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C11" s="15">
         <v>6</v>
@@ -4633,7 +4638,7 @@
         <v>20</v>
       </c>
       <c r="E11" s="25" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="F11" s="15">
         <f t="shared" si="0"/>
@@ -4647,7 +4652,7 @@
         <v>1</v>
       </c>
       <c r="J11" s="19" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="K11" s="15" t="str">
         <f t="shared" si="3"/>
@@ -4679,12 +4684,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="20" customFormat="1" ht="17">
+    <row r="12" spans="1:24" s="20" customFormat="1" x14ac:dyDescent="0.35">
       <c r="A12" s="26">
         <v>100303</v>
       </c>
       <c r="B12" s="25" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C12" s="15">
         <v>7</v>
@@ -4693,7 +4698,7 @@
         <v>20</v>
       </c>
       <c r="E12" s="25" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F12" s="15">
         <f t="shared" si="0"/>
@@ -4707,7 +4712,7 @@
         <v>1</v>
       </c>
       <c r="J12" s="31" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="K12" s="27" t="str">
         <f t="shared" ref="K12:K17" si="5">"{"&amp;O12&amp;"}"</f>
@@ -4739,12 +4744,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:24" ht="17">
+    <row r="13" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A13" s="24">
         <v>100001</v>
       </c>
       <c r="B13" s="25" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="C13" s="15">
         <v>8</v>
@@ -4753,7 +4758,7 @@
         <v>20</v>
       </c>
       <c r="E13" s="25" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F13" s="15">
         <f t="shared" si="0"/>
@@ -4767,7 +4772,7 @@
         <v>1</v>
       </c>
       <c r="J13" s="19" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="K13" s="15" t="str">
         <f t="shared" ref="K13:K14" si="7">"{"&amp;O13&amp;"}"</f>
@@ -4799,12 +4804,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:24">
+    <row r="14" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A14" s="24">
         <v>100002</v>
       </c>
       <c r="B14" s="25" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="C14" s="15">
         <v>9</v>
@@ -4813,7 +4818,7 @@
         <v>20</v>
       </c>
       <c r="E14" s="25" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F14" s="15">
         <f t="shared" si="0"/>
@@ -4827,7 +4832,7 @@
         <v>1</v>
       </c>
       <c r="J14" s="8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="K14" s="15" t="str">
         <f t="shared" si="7"/>
@@ -4859,12 +4864,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:24">
+    <row r="15" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A15" s="24">
         <v>100003</v>
       </c>
       <c r="B15" s="25" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="C15" s="15">
         <v>10</v>
@@ -4873,7 +4878,7 @@
         <v>20</v>
       </c>
       <c r="E15" s="25" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F15" s="15">
         <f t="shared" si="0"/>
@@ -4887,7 +4892,7 @@
         <v>1</v>
       </c>
       <c r="J15" s="8" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="K15" s="15" t="str">
         <f t="shared" ref="K15" si="9">"{"&amp;O15&amp;"}"</f>
@@ -4897,7 +4902,7 @@
         <v>0</v>
       </c>
       <c r="M15" s="29" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="N15" s="9">
         <v>1</v>
@@ -4921,12 +4926,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:24" ht="17">
+    <row r="16" spans="1:24" x14ac:dyDescent="0.35">
       <c r="A16" s="24">
         <v>100304</v>
       </c>
       <c r="B16" s="25" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C16" s="15">
         <v>11</v>
@@ -4935,7 +4940,7 @@
         <v>20</v>
       </c>
       <c r="E16" s="25" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F16" s="15">
         <f t="shared" si="0"/>
@@ -4949,7 +4954,7 @@
         <v>1</v>
       </c>
       <c r="J16" s="19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="K16" s="15" t="str">
         <f t="shared" si="5"/>
@@ -4981,12 +4986,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:23" ht="17">
+    <row r="17" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A17" s="24">
         <v>1013</v>
       </c>
       <c r="B17" s="25" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="C17" s="15">
         <v>12</v>
@@ -4995,7 +5000,7 @@
         <v>20</v>
       </c>
       <c r="E17" s="25" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F17" s="15"/>
       <c r="G17" s="19"/>
@@ -5006,7 +5011,7 @@
         <v>0</v>
       </c>
       <c r="J17" s="19" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="K17" s="15" t="str">
         <f t="shared" si="5"/>
@@ -5053,26 +5058,26 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:W16"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17.1640625" style="9" customWidth="1"/>
-    <col min="2" max="3" width="17.83203125" style="9" customWidth="1"/>
-    <col min="4" max="5" width="15.1640625" style="9" customWidth="1"/>
-    <col min="6" max="6" width="19.83203125" style="9" customWidth="1"/>
+    <col min="1" max="1" width="17.125" style="9" customWidth="1"/>
+    <col min="2" max="3" width="17.875" style="9" customWidth="1"/>
+    <col min="4" max="5" width="15.125" style="9" customWidth="1"/>
+    <col min="6" max="6" width="19.875" style="9" customWidth="1"/>
     <col min="7" max="7" width="28" style="9" customWidth="1"/>
-    <col min="8" max="8" width="15.1640625" style="9" customWidth="1"/>
-    <col min="9" max="9" width="23.1640625" style="9" customWidth="1"/>
-    <col min="10" max="10" width="16.1640625" style="9" customWidth="1"/>
-    <col min="11" max="11" width="63.1640625" style="9" customWidth="1"/>
-    <col min="12" max="12" width="20.1640625" style="9" customWidth="1"/>
-    <col min="13" max="13" width="13.1640625" style="9" customWidth="1"/>
+    <col min="8" max="8" width="15.125" style="9" customWidth="1"/>
+    <col min="9" max="9" width="23.125" style="9" customWidth="1"/>
+    <col min="10" max="10" width="16.125" style="9" customWidth="1"/>
+    <col min="11" max="11" width="63.125" style="9" customWidth="1"/>
+    <col min="12" max="12" width="20.125" style="9" customWidth="1"/>
+    <col min="13" max="13" width="13.125" style="9" customWidth="1"/>
     <col min="14" max="14" width="9" style="9"/>
-    <col min="15" max="15" width="13.1640625" style="9" customWidth="1"/>
+    <col min="15" max="15" width="13.125" style="9" customWidth="1"/>
     <col min="16" max="16" width="11" style="9" customWidth="1"/>
     <col min="17" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5080,7 +5085,7 @@
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D1" s="2" t="s">
         <v>73</v>
@@ -5089,7 +5094,7 @@
         <v>74</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="G1" s="2" t="s">
         <v>75</v>
@@ -5140,7 +5145,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="2" spans="1:23">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>22</v>
       </c>
@@ -5154,7 +5159,7 @@
         <v>22</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>94</v>
+        <v>262</v>
       </c>
       <c r="F2" s="2" t="s">
         <v>11</v>
@@ -5163,19 +5168,19 @@
         <v>11</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>11</v>
       </c>
       <c r="J2" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="K2" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>98</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>99</v>
       </c>
       <c r="M2" s="2" t="s">
         <v>11</v>
@@ -5184,7 +5189,7 @@
         <v>10</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="P2" s="1" t="s">
         <v>11</v>
@@ -5208,7 +5213,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:23">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -5219,7 +5224,7 @@
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
@@ -5228,13 +5233,13 @@
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
       <c r="M3" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="P3" s="1" t="s">
         <v>13</v>
@@ -5259,7 +5264,7 @@
       </c>
       <c r="W3" s="1"/>
     </row>
-    <row r="4" spans="1:23">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -5282,7 +5287,7 @@
         <v>13</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>13</v>
@@ -5294,7 +5299,7 @@
         <v>13</v>
       </c>
       <c r="L4" s="2" t="s">
-        <v>104</v>
+        <v>263</v>
       </c>
       <c r="M4" s="2" t="s">
         <v>13</v>
@@ -5328,79 +5333,79 @@
       </c>
       <c r="W4" s="12"/>
     </row>
-    <row r="5" spans="1:23">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="D5" s="7" t="s">
         <v>105</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>106</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>18</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G5" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="H5" s="7" t="s">
         <v>107</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="I5" s="7" t="s">
         <v>108</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="J5" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="K5" s="13" t="s">
         <v>110</v>
       </c>
-      <c r="K5" s="13" t="s">
+      <c r="L5" s="13" t="s">
         <v>111</v>
       </c>
-      <c r="L5" s="13" t="s">
+      <c r="M5" s="13" t="s">
         <v>112</v>
-      </c>
-      <c r="M5" s="13" t="s">
-        <v>113</v>
       </c>
       <c r="N5" s="13"/>
       <c r="O5" s="13" t="s">
+        <v>113</v>
+      </c>
+      <c r="P5" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="P5" s="8" t="s">
+      <c r="Q5" s="9" t="s">
         <v>115</v>
       </c>
-      <c r="Q5" s="9" t="s">
+      <c r="R5" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="R5" s="9" t="s">
+      <c r="S5" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="S5" s="9" t="s">
+      <c r="T5" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="U5" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="T5" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="U5" s="9" t="s">
-        <v>119</v>
-      </c>
       <c r="V5" s="9" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="6" spans="1:23">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A6" s="9">
         <f t="shared" ref="A6:A16" si="0">200000+C6*100+D6</f>
         <v>200101</v>
       </c>
       <c r="B6" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C6" s="6">
         <f>COUNTIF($D$6:D6,1)</f>
@@ -5413,7 +5418,7 @@
         <v>24</v>
       </c>
       <c r="F6" s="6" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="G6" s="6" t="str">
         <f>"支线·"&amp;F6</f>
@@ -5427,7 +5432,7 @@
         <v>0</v>
       </c>
       <c r="K6" s="6" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="L6" s="15" t="str">
         <f t="shared" ref="L6:L16" si="1">"{"&amp;P6&amp;"}"</f>
@@ -5451,13 +5456,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:23">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A7" s="9">
         <f t="shared" si="0"/>
         <v>200102</v>
       </c>
       <c r="B7" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C7" s="6">
         <v>1</v>
@@ -5469,7 +5474,7 @@
         <v>24</v>
       </c>
       <c r="F7" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="G7" s="6" t="str">
         <f t="shared" ref="G7:G16" si="3">"支线·"&amp;F7</f>
@@ -5507,13 +5512,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:23">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A8" s="9">
         <f t="shared" si="0"/>
         <v>200103</v>
       </c>
       <c r="B8" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C8" s="6">
         <v>1</v>
@@ -5525,7 +5530,7 @@
         <v>24</v>
       </c>
       <c r="F8" s="6" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="G8" s="6" t="str">
         <f t="shared" si="3"/>
@@ -5542,7 +5547,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="6" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="L8" s="15" t="str">
         <f t="shared" si="1"/>
@@ -5566,13 +5571,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:23">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A9" s="9">
         <f t="shared" si="0"/>
         <v>200104</v>
       </c>
       <c r="B9" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C9" s="6">
         <v>1</v>
@@ -5584,7 +5589,7 @@
         <v>24</v>
       </c>
       <c r="F9" s="6" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="G9" s="6" t="str">
         <f t="shared" si="3"/>
@@ -5598,7 +5603,7 @@
         <v>0</v>
       </c>
       <c r="K9" s="6" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="L9" s="15" t="str">
         <f t="shared" si="1"/>
@@ -5622,13 +5627,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:23">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A10" s="9">
         <f t="shared" si="0"/>
         <v>200105</v>
       </c>
       <c r="B10" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C10" s="6">
         <v>1</v>
@@ -5640,7 +5645,7 @@
         <v>24</v>
       </c>
       <c r="F10" s="6" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G10" s="6" t="str">
         <f t="shared" si="3"/>
@@ -5654,7 +5659,7 @@
         <v>0</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="L10" s="15" t="str">
         <f t="shared" si="1"/>
@@ -5678,13 +5683,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:23">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A11" s="9">
         <f t="shared" si="0"/>
         <v>200106</v>
       </c>
       <c r="B11" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C11" s="6">
         <v>1</v>
@@ -5696,7 +5701,7 @@
         <v>24</v>
       </c>
       <c r="F11" s="6" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G11" s="6" t="str">
         <f t="shared" si="3"/>
@@ -5710,7 +5715,7 @@
         <v>0</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="L11" s="15" t="str">
         <f t="shared" si="1"/>
@@ -5734,13 +5739,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:23">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A12" s="9">
         <f t="shared" si="0"/>
         <v>200107</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C12" s="6">
         <v>1</v>
@@ -5752,7 +5757,7 @@
         <v>24</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="G12" s="6" t="str">
         <f t="shared" si="3"/>
@@ -5766,7 +5771,7 @@
         <v>0</v>
       </c>
       <c r="K12" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="L12" s="15" t="str">
         <f t="shared" si="1"/>
@@ -5790,13 +5795,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:23">
+    <row r="13" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A13" s="9">
         <f t="shared" si="0"/>
         <v>200201</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C13" s="6">
         <v>2</v>
@@ -5808,7 +5813,7 @@
         <v>24</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="G13" s="6" t="str">
         <f t="shared" si="3"/>
@@ -5825,7 +5830,7 @@
         <v>0</v>
       </c>
       <c r="K13" s="6" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="L13" s="15" t="str">
         <f t="shared" si="1"/>
@@ -5849,13 +5854,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:23">
+    <row r="14" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A14" s="9">
         <f t="shared" si="0"/>
         <v>200202</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C14" s="6">
         <v>2</v>
@@ -5867,7 +5872,7 @@
         <v>24</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="G14" s="6" t="str">
         <f t="shared" si="3"/>
@@ -5884,7 +5889,7 @@
         <v>0</v>
       </c>
       <c r="K14" s="6" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="L14" s="15" t="str">
         <f t="shared" si="1"/>
@@ -5908,13 +5913,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:23">
+    <row r="15" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A15" s="9">
         <f t="shared" si="0"/>
         <v>200203</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C15" s="6">
         <v>2</v>
@@ -5926,7 +5931,7 @@
         <v>24</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G15" s="6" t="str">
         <f t="shared" si="3"/>
@@ -5943,7 +5948,7 @@
         <v>0</v>
       </c>
       <c r="K15" s="6" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="L15" s="15" t="str">
         <f t="shared" si="1"/>
@@ -5967,13 +5972,13 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:23">
+    <row r="16" spans="1:23" x14ac:dyDescent="0.35">
       <c r="A16" s="9">
         <f t="shared" si="0"/>
         <v>200204</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C16" s="6">
         <v>2</v>
@@ -5985,7 +5990,7 @@
         <v>24</v>
       </c>
       <c r="F16" s="6" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G16" s="6" t="str">
         <f t="shared" si="3"/>
@@ -5999,7 +6004,7 @@
         <v>0</v>
       </c>
       <c r="K16" s="6" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="L16" s="15" t="str">
         <f t="shared" si="1"/>
@@ -6037,16 +6042,16 @@
     <tabColor theme="5" tint="0.39915158543656726"/>
   </sheetPr>
   <dimension ref="A1:I19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="17.1640625" customWidth="1"/>
-    <col min="3" max="3" width="15.1640625" style="9" customWidth="1"/>
-    <col min="4" max="7" width="17.1640625" customWidth="1"/>
-    <col min="8" max="8" width="20.1640625" customWidth="1"/>
-    <col min="9" max="9" width="13.1640625" style="9" customWidth="1"/>
+    <col min="1" max="2" width="17.125" customWidth="1"/>
+    <col min="3" max="3" width="15.125" style="9" customWidth="1"/>
+    <col min="4" max="7" width="17.125" customWidth="1"/>
+    <col min="8" max="8" width="20.125" customWidth="1"/>
+    <col min="9" max="9" width="13.125" style="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6075,7 +6080,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>22</v>
       </c>
@@ -6095,16 +6100,16 @@
         <v>11</v>
       </c>
       <c r="G2" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>98</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>99</v>
       </c>
       <c r="I2" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -6115,17 +6120,17 @@
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -6148,47 +6153,47 @@
         <v>13</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I4" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>105</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>106</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G5" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="H5" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="I5" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="I5" s="7" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
+    </row>
+    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="B6" s="5" t="s">
         <v>177</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>178</v>
       </c>
       <c r="C6" s="6">
         <v>1</v>
@@ -6197,27 +6202,27 @@
         <v>4</v>
       </c>
       <c r="E6" s="6" t="s">
+        <v>178</v>
+      </c>
+      <c r="F6" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="F6" s="6" t="s">
+      <c r="G6" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="H6" s="6" t="s">
         <v>181</v>
-      </c>
-      <c r="H6" s="6" t="s">
-        <v>182</v>
       </c>
       <c r="I6" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
+        <v>182</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>183</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>184</v>
       </c>
       <c r="C7" s="6">
         <v>2</v>
@@ -6226,27 +6231,27 @@
         <v>4</v>
       </c>
       <c r="E7" s="6" t="s">
+        <v>184</v>
+      </c>
+      <c r="F7" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="G7" s="6" t="s">
         <v>185</v>
       </c>
-      <c r="F7" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="G7" s="6" t="s">
+      <c r="H7" s="6" t="s">
         <v>186</v>
-      </c>
-      <c r="H7" s="6" t="s">
-        <v>187</v>
       </c>
       <c r="I7" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
+        <v>187</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>188</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>189</v>
       </c>
       <c r="C8" s="6">
         <v>3</v>
@@ -6255,27 +6260,27 @@
         <v>4</v>
       </c>
       <c r="E8" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="F8" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="G8" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="F8" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="G8" s="6" t="s">
+      <c r="H8" s="6" t="s">
         <v>191</v>
-      </c>
-      <c r="H8" s="6" t="s">
-        <v>192</v>
       </c>
       <c r="I8" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
+        <v>192</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>193</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>194</v>
       </c>
       <c r="C9" s="6">
         <v>4</v>
@@ -6284,22 +6289,22 @@
         <v>4</v>
       </c>
       <c r="E9" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>179</v>
+      </c>
+      <c r="G9" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="F9" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="G9" s="6" t="s">
+      <c r="H9" s="6" t="s">
         <v>196</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>197</v>
       </c>
       <c r="I9" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A10" s="4"/>
       <c r="B10" s="5"/>
       <c r="C10" s="6"/>
@@ -6310,7 +6315,7 @@
       <c r="H10" s="6"/>
       <c r="I10" s="6"/>
     </row>
-    <row r="11" spans="1:9">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" s="4"/>
       <c r="B11" s="5"/>
       <c r="C11" s="6"/>
@@ -6321,7 +6326,7 @@
       <c r="H11" s="6"/>
       <c r="I11" s="6"/>
     </row>
-    <row r="12" spans="1:9">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" s="4"/>
       <c r="B12" s="5"/>
       <c r="C12" s="6"/>
@@ -6332,7 +6337,7 @@
       <c r="H12" s="6"/>
       <c r="I12" s="6"/>
     </row>
-    <row r="13" spans="1:9">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" s="4"/>
       <c r="B13" s="5"/>
       <c r="C13" s="6"/>
@@ -6343,7 +6348,7 @@
       <c r="H13" s="6"/>
       <c r="I13" s="6"/>
     </row>
-    <row r="14" spans="1:9">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A14" s="4"/>
       <c r="B14" s="5"/>
       <c r="C14" s="6"/>
@@ -6354,7 +6359,7 @@
       <c r="H14" s="6"/>
       <c r="I14" s="6"/>
     </row>
-    <row r="15" spans="1:9">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" s="4"/>
       <c r="B15" s="5"/>
       <c r="C15" s="6"/>
@@ -6365,7 +6370,7 @@
       <c r="H15" s="6"/>
       <c r="I15" s="6"/>
     </row>
-    <row r="16" spans="1:9">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" s="4"/>
       <c r="B16" s="5"/>
       <c r="C16" s="6"/>
@@ -6376,7 +6381,7 @@
       <c r="H16" s="6"/>
       <c r="I16" s="6"/>
     </row>
-    <row r="17" spans="1:9">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A17" s="4"/>
       <c r="B17" s="5"/>
       <c r="C17" s="6"/>
@@ -6387,7 +6392,7 @@
       <c r="H17" s="6"/>
       <c r="I17" s="6"/>
     </row>
-    <row r="18" spans="1:9">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A18" s="4"/>
       <c r="B18" s="5"/>
       <c r="C18" s="6"/>
@@ -6398,7 +6403,7 @@
       <c r="H18" s="6"/>
       <c r="I18" s="6"/>
     </row>
-    <row r="19" spans="1:9">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A19" s="4"/>
       <c r="B19" s="5"/>
       <c r="C19" s="6"/>
@@ -6422,17 +6427,17 @@
     <tabColor theme="5" tint="0.39915158543656726"/>
   </sheetPr>
   <dimension ref="A1:J19"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="17.1640625" defaultRowHeight="16"/>
+  <sheetFormatPr defaultColWidth="17.125" defaultRowHeight="16.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="2" width="17.1640625" customWidth="1"/>
-    <col min="3" max="3" width="15.1640625" style="9" customWidth="1"/>
-    <col min="4" max="7" width="17.1640625" customWidth="1"/>
-    <col min="8" max="9" width="25.6640625" customWidth="1"/>
-    <col min="10" max="10" width="13.1640625" style="9" customWidth="1"/>
-    <col min="11" max="16377" width="17.1640625" customWidth="1"/>
+    <col min="1" max="2" width="17.125" customWidth="1"/>
+    <col min="3" max="3" width="15.125" style="9" customWidth="1"/>
+    <col min="4" max="7" width="17.125" customWidth="1"/>
+    <col min="8" max="9" width="25.625" customWidth="1"/>
+    <col min="10" max="10" width="13.125" style="9" customWidth="1"/>
+    <col min="11" max="16377" width="17.125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6458,13 +6463,13 @@
         <v>80</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="J1" s="2" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>22</v>
       </c>
@@ -6484,19 +6489,19 @@
         <v>11</v>
       </c>
       <c r="G2" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>99</v>
-      </c>
       <c r="I2" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="J2" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -6507,18 +6512,18 @@
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
       <c r="F3" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
       <c r="J3" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -6541,53 +6546,53 @@
         <v>13</v>
       </c>
       <c r="H4" s="2" t="s">
+        <v>259</v>
+      </c>
+      <c r="I4" s="2" t="s">
         <v>260</v>
       </c>
-      <c r="I4" s="2" t="s">
-        <v>261</v>
-      </c>
       <c r="J4" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:10">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>105</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>106</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G5" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="H5" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="H5" s="7" t="s">
+      <c r="I5" s="7" t="s">
+        <v>198</v>
+      </c>
+      <c r="J5" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="I5" s="7" t="s">
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="J5" s="7" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
-      <c r="A6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>200</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>201</v>
       </c>
       <c r="C6" s="6">
         <v>1</v>
@@ -6605,21 +6610,21 @@
         <v>45</v>
       </c>
       <c r="H6" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="I6" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="J6" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
+        <v>201</v>
+      </c>
+      <c r="B7" s="5" t="s">
         <v>202</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>203</v>
       </c>
       <c r="C7" s="6">
         <v>2</v>
@@ -6628,30 +6633,30 @@
         <v>5</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="F7" s="6" t="s">
         <v>43</v>
       </c>
       <c r="G7" s="6" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H7" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="I7" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="J7" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
+        <v>205</v>
+      </c>
+      <c r="B8" s="5" t="s">
         <v>206</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>207</v>
       </c>
       <c r="C8" s="6">
         <v>3</v>
@@ -6660,30 +6665,30 @@
         <v>5</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F8" s="6" t="s">
         <v>43</v>
       </c>
       <c r="G8" s="6" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H8" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="I8" s="6" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="J8" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="B9" s="5" t="s">
         <v>210</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>211</v>
       </c>
       <c r="C9" s="6">
         <v>4</v>
@@ -6692,25 +6697,25 @@
         <v>5</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="F9" s="6" t="s">
         <v>43</v>
       </c>
       <c r="G9" s="6" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H9" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="I9" s="6" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="J9" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="4"/>
       <c r="B10" s="5"/>
       <c r="C10" s="6"/>
@@ -6722,7 +6727,7 @@
       <c r="I10" s="6"/>
       <c r="J10" s="6"/>
     </row>
-    <row r="11" spans="1:10">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" s="4"/>
       <c r="B11" s="5"/>
       <c r="C11" s="6"/>
@@ -6734,7 +6739,7 @@
       <c r="I11" s="6"/>
       <c r="J11" s="6"/>
     </row>
-    <row r="12" spans="1:10">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="4"/>
       <c r="B12" s="5"/>
       <c r="C12" s="6"/>
@@ -6746,7 +6751,7 @@
       <c r="I12" s="6"/>
       <c r="J12" s="6"/>
     </row>
-    <row r="13" spans="1:10">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A13" s="4"/>
       <c r="B13" s="5"/>
       <c r="C13" s="6"/>
@@ -6758,7 +6763,7 @@
       <c r="I13" s="6"/>
       <c r="J13" s="6"/>
     </row>
-    <row r="14" spans="1:10">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="4"/>
       <c r="B14" s="5"/>
       <c r="C14" s="6"/>
@@ -6770,19 +6775,19 @@
       <c r="I14" s="6"/>
       <c r="J14" s="6"/>
     </row>
-    <row r="15" spans="1:10">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="J15" s="6"/>
     </row>
-    <row r="16" spans="1:10">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="J16" s="6"/>
     </row>
-    <row r="17" spans="10:10">
+    <row r="17" spans="10:10" x14ac:dyDescent="0.35">
       <c r="J17" s="6"/>
     </row>
-    <row r="18" spans="10:10">
+    <row r="18" spans="10:10" x14ac:dyDescent="0.35">
       <c r="J18" s="6"/>
     </row>
-    <row r="19" spans="10:10">
+    <row r="19" spans="10:10" x14ac:dyDescent="0.35">
       <c r="J19" s="6"/>
     </row>
   </sheetData>
@@ -6795,18 +6800,18 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:L9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="4" max="4" width="10.6640625" customWidth="1"/>
+    <col min="4" max="4" width="10.625" customWidth="1"/>
     <col min="5" max="5" width="29" customWidth="1"/>
-    <col min="6" max="6" width="20.83203125" customWidth="1"/>
-    <col min="7" max="7" width="16.6640625" customWidth="1"/>
-    <col min="9" max="9" width="35.6640625" customWidth="1"/>
-    <col min="10" max="10" width="21.83203125" customWidth="1"/>
+    <col min="6" max="6" width="20.875" customWidth="1"/>
+    <col min="7" max="7" width="16.625" customWidth="1"/>
+    <col min="9" max="9" width="35.625" customWidth="1"/>
+    <col min="10" max="10" width="21.875" customWidth="1"/>
     <col min="12" max="12" width="52" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="16">
+    <row r="1" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6844,7 +6849,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="16">
+    <row r="2" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
         <v>22</v>
       </c>
@@ -6861,28 +6866,28 @@
         <v>11</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>11</v>
       </c>
       <c r="H2" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="I2" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>98</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>99</v>
       </c>
       <c r="K2" s="2" t="s">
         <v>11</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="16">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -6894,19 +6899,19 @@
       <c r="E3" s="2"/>
       <c r="F3" s="2"/>
       <c r="G3" s="2" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="H3" s="2"/>
       <c r="I3" s="2"/>
       <c r="J3" s="2"/>
       <c r="K3" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="16">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -6923,7 +6928,7 @@
         <v>13</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>13</v>
@@ -6935,7 +6940,7 @@
         <v>13</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="K4" s="2" t="s">
         <v>13</v>
@@ -6944,50 +6949,50 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="16">
+    <row r="5" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
       <c r="B5" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>105</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>106</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>18</v>
       </c>
       <c r="E5" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="G5" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="H5" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="I5" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="I5" s="7" t="s">
+      <c r="J5" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="J5" s="7" t="s">
+      <c r="K5" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="K5" s="7" t="s">
-        <v>113</v>
-      </c>
       <c r="L5" s="7" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A6" s="4" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="6" spans="1:12" ht="16">
-      <c r="A6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>215</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>216</v>
       </c>
       <c r="C6" s="6">
         <v>2</v>
@@ -6996,7 +7001,7 @@
         <v>7</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F6" s="6"/>
       <c r="G6" s="6" t="s">
@@ -7004,24 +7009,24 @@
       </c>
       <c r="H6" s="6"/>
       <c r="I6" s="6" t="s">
+        <v>217</v>
+      </c>
+      <c r="J6" s="6" t="s">
         <v>218</v>
-      </c>
-      <c r="J6" s="6" t="s">
-        <v>219</v>
       </c>
       <c r="K6" s="6">
         <v>0</v>
       </c>
       <c r="L6" s="8" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A7" s="4" t="s">
         <v>220</v>
       </c>
-    </row>
-    <row r="7" spans="1:12" ht="16">
-      <c r="A7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>221</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>222</v>
       </c>
       <c r="C7" s="6">
         <v>3</v>
@@ -7030,7 +7035,7 @@
         <v>7</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F7" s="6"/>
       <c r="G7" s="6" t="s">
@@ -7038,24 +7043,24 @@
       </c>
       <c r="H7" s="6"/>
       <c r="I7" s="6" t="s">
+        <v>222</v>
+      </c>
+      <c r="J7" s="6" t="s">
         <v>223</v>
-      </c>
-      <c r="J7" s="6" t="s">
-        <v>224</v>
       </c>
       <c r="K7" s="6">
         <v>0</v>
       </c>
       <c r="L7" s="8" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A8" s="4" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="8" spans="1:12" ht="16">
-      <c r="A8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>226</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>227</v>
       </c>
       <c r="C8" s="6">
         <v>4</v>
@@ -7064,7 +7069,7 @@
         <v>7</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F8" s="6"/>
       <c r="G8" s="6" t="s">
@@ -7072,24 +7077,24 @@
       </c>
       <c r="H8" s="6"/>
       <c r="I8" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="J8" s="6" t="s">
         <v>228</v>
-      </c>
-      <c r="J8" s="6" t="s">
-        <v>229</v>
       </c>
       <c r="K8" s="6">
         <v>0</v>
       </c>
       <c r="L8" s="8" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="16.5" x14ac:dyDescent="0.35">
+      <c r="A9" s="4" t="s">
         <v>230</v>
       </c>
-    </row>
-    <row r="9" spans="1:12" ht="16">
-      <c r="A9" s="4" t="s">
-        <v>231</v>
-      </c>
       <c r="B9" s="5" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="C9" s="6">
         <v>5</v>
@@ -7098,7 +7103,7 @@
         <v>7</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="F9" s="6"/>
       <c r="G9" s="6" t="s">
@@ -7106,16 +7111,16 @@
       </c>
       <c r="H9" s="6"/>
       <c r="I9" s="6" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="K9" s="6">
         <v>0</v>
       </c>
       <c r="L9" s="8" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
   </sheetData>

--- a/test/res/task.xlsx
+++ b/test/res/task.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\bite\Desktop\github\xlsx-exporter\test\res\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/codetypes/Desktop/Github/xlsx-exporter/test/res/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{718CF2AC-EFC2-455B-8CF6-1B8D933B94F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AAD05018-5370-084E-938D-63CC0632BB15}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-32100" yWindow="1425" windowWidth="28395" windowHeight="18960" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="680" windowWidth="30240" windowHeight="17680" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="define" sheetId="9" r:id="rId1"/>
@@ -1065,6 +1065,841 @@
     <author>Administrator</author>
   </authors>
   <commentList>
+    <comment ref="J5" authorId="0" shapeId="0" xr:uid="{2F804BCD-7389-9449-8311-A622B2319027}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>主线类型</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>type</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>：</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">        KILL_WOOD = 1,          -- </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>砍死一棵树</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">        KILL_FOOD = 2,          -- </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>割一片小麦</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">        RESCUS_SOLDIER = 3,     -- </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>解救士兵</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">        PICK_CHEST = 4,         -- </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>捡宝箱</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">        TALK_TO_NPC = 5,        -- </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>与</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>NPC</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>对话（可指定</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Npc id:&lt;battle_npc&gt;</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>）</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">        KILL_MONSTER_TROOP = 6, -- </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>击杀怪物队伍（可指定队伍</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>id:&lt;monster.troop&gt;</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>）</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">        KILL_ANY_MONSTER_TROOP = 7, -- </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>击杀任意怪物队伍</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">        UPGRADE_BUILDING = 8,   -- </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>建造或者升级指定建筑（可指定建筑</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>id:&lt;battle_building&gt;</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>）</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">        UNLOCK_CLOUD = 9,       -- </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>解锁指定迷雾（可指定迷雾</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>id:&lt;1~n&gt;</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>）</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">        KILL_STONE = 10,         -- </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>采集一组矿</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">        COLLECT_ONE_WOOD = 11,  -- </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>采集一个木头资源</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">        COLLECT_ONE_FOOD = 12,  -- </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>采集一个粮食资源</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">        COLLECT_ONE_STONE = 13, -- </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>采集一个矿石资源</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">        COLLECT_ONE_ANY = 14,   -- </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>采集一个木头</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>/</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>粮食</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>/</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>矿石</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">        UNLOCK_ANY_CLOUD = 15,       -- </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>解锁任意指定迷雾</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">        FINISH_PLOT_THEATRE = 16  --</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>完成剧情对话，填</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>plot_theatre</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>表</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">ID 
+</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">        KILL_SCENARIO_MONSTER_TROOP = 18  -- </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>击杀舞台剧怪物队伍</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>(</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>可指定队伍</t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color rgb="FF000000"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">id:&lt;monster.scenario_troop&gt;)
+</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments4.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Administrator</author>
+  </authors>
+  <commentList>
     <comment ref="I5" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0700-000001000000}">
       <text>
         <r>
@@ -1101,7 +1936,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="739" uniqueCount="270">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="745" uniqueCount="274">
   <si>
     <t>id</t>
   </si>
@@ -1925,17 +2760,29 @@
   <si>
     <t>@define;@stringify(task)</t>
     <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>{kind:"kill_monster",count: 1,id:5}</t>
+  </si>
+  <si>
+    <t>{kind:"collect_coin",count:1,id:71001,duration:2}</t>
+  </si>
+  <si>
+    <t>task_args</t>
+  </si>
+  <si>
+    <t>TaskArgs?</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
@@ -1964,7 +2811,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1984,7 +2831,7 @@
     </font>
     <font>
       <sz val="9"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -2264,7 +3111,7 @@
     </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="常规 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000031000000}"/>
     <cellStyle name="常规 3" xfId="2" xr:uid="{00000000-0005-0000-0000-000032000000}"/>
   </cellStyles>
@@ -3190,17 +4037,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I24"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="14.625" customWidth="1"/>
-    <col min="3" max="3" width="16.625" customWidth="1"/>
-    <col min="4" max="4" width="25.625" customWidth="1"/>
-    <col min="5" max="5" width="45.875" customWidth="1"/>
-    <col min="6" max="6" width="18.625" customWidth="1"/>
-    <col min="8" max="9" width="12.625" customWidth="1"/>
+    <col min="2" max="2" width="14.6640625" customWidth="1"/>
+    <col min="3" max="3" width="16.6640625" customWidth="1"/>
+    <col min="4" max="4" width="25.6640625" customWidth="1"/>
+    <col min="5" max="5" width="45.83203125" customWidth="1"/>
+    <col min="6" max="6" width="18.6640625" customWidth="1"/>
+    <col min="8" max="9" width="12.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9">
       <c r="A1" s="40" t="s">
         <v>269</v>
       </c>
@@ -3210,7 +4057,7 @@
       <c r="E1" s="41"/>
       <c r="F1" s="41"/>
     </row>
-    <row r="2" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" ht="16">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -3239,7 +4086,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="3" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" ht="16">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -3268,7 +4115,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="4" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" ht="16">
       <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
@@ -3283,7 +4130,7 @@
       <c r="H4" s="32"/>
       <c r="I4" s="32"/>
     </row>
-    <row r="5" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" ht="16">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -3312,7 +4159,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:9" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" ht="16">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -3329,7 +4176,7 @@
       <c r="H6" s="32"/>
       <c r="I6" s="32"/>
     </row>
-    <row r="7" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:9" ht="16">
       <c r="A7" s="21" t="s">
         <v>17</v>
       </c>
@@ -3358,7 +4205,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="8" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:9" ht="16">
       <c r="A8" s="21" t="s">
         <v>17</v>
       </c>
@@ -3381,7 +4228,7 @@
       <c r="H8" s="33"/>
       <c r="I8" s="33"/>
     </row>
-    <row r="9" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" ht="16">
       <c r="A9" s="21" t="s">
         <v>17</v>
       </c>
@@ -3404,7 +4251,7 @@
       <c r="H9" s="33"/>
       <c r="I9" s="33"/>
     </row>
-    <row r="10" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:9" ht="16">
       <c r="A10" s="21" t="s">
         <v>17</v>
       </c>
@@ -3427,7 +4274,7 @@
       <c r="H10" s="33"/>
       <c r="I10" s="33"/>
     </row>
-    <row r="11" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" ht="16">
       <c r="A11" s="21" t="s">
         <v>17</v>
       </c>
@@ -3450,7 +4297,7 @@
       <c r="H11" s="33"/>
       <c r="I11" s="33"/>
     </row>
-    <row r="12" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" ht="16">
       <c r="A12" s="21" t="s">
         <v>17</v>
       </c>
@@ -3473,7 +4320,7 @@
       <c r="H12" s="33"/>
       <c r="I12" s="33"/>
     </row>
-    <row r="13" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" ht="16">
       <c r="A13" s="21" t="s">
         <v>17</v>
       </c>
@@ -3496,7 +4343,7 @@
       <c r="H13" s="33"/>
       <c r="I13" s="33"/>
     </row>
-    <row r="14" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:9" ht="16">
       <c r="A14" s="21" t="s">
         <v>17</v>
       </c>
@@ -3523,7 +4370,7 @@
       </c>
       <c r="I14" s="33"/>
     </row>
-    <row r="15" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" ht="16">
       <c r="A15" s="21" t="s">
         <v>17</v>
       </c>
@@ -3546,7 +4393,7 @@
       <c r="H15" s="33"/>
       <c r="I15" s="33"/>
     </row>
-    <row r="16" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" ht="16">
       <c r="A16" s="21" t="s">
         <v>17</v>
       </c>
@@ -3569,7 +4416,7 @@
       <c r="H16" s="33"/>
       <c r="I16" s="33"/>
     </row>
-    <row r="17" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9" ht="16">
       <c r="A17" s="21" t="s">
         <v>17</v>
       </c>
@@ -3592,7 +4439,7 @@
       <c r="H17" s="33"/>
       <c r="I17" s="33"/>
     </row>
-    <row r="18" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9" ht="16">
       <c r="A18" s="21" t="s">
         <v>17</v>
       </c>
@@ -3615,7 +4462,7 @@
       <c r="H18" s="33"/>
       <c r="I18" s="33"/>
     </row>
-    <row r="19" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9" ht="16">
       <c r="A19" s="21" t="s">
         <v>17</v>
       </c>
@@ -3638,7 +4485,7 @@
       <c r="H19" s="33"/>
       <c r="I19" s="33"/>
     </row>
-    <row r="20" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:9" ht="16">
       <c r="A20" s="21" t="s">
         <v>17</v>
       </c>
@@ -3665,7 +4512,7 @@
       </c>
       <c r="I20" s="33"/>
     </row>
-    <row r="21" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:9" ht="16">
       <c r="A21" s="21" t="s">
         <v>17</v>
       </c>
@@ -3688,7 +4535,7 @@
       <c r="H21" s="33"/>
       <c r="I21" s="33"/>
     </row>
-    <row r="22" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:9" ht="16">
       <c r="A22" s="21" t="s">
         <v>17</v>
       </c>
@@ -3711,7 +4558,7 @@
       <c r="H22" s="33"/>
       <c r="I22" s="33"/>
     </row>
-    <row r="23" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:9" ht="16">
       <c r="A23" s="21" t="s">
         <v>17</v>
       </c>
@@ -3734,7 +4581,7 @@
       <c r="H23" s="33"/>
       <c r="I23" s="33"/>
     </row>
-    <row r="24" spans="1:9" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:9" ht="16">
       <c r="A24" s="21" t="s">
         <v>17</v>
       </c>
@@ -3770,16 +4617,16 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{984B885C-48D0-4D9B-AAB3-39C5F463E278}">
   <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="9" style="39"/>
     <col min="2" max="2" width="32.5" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="9.6640625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="49" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:5">
       <c r="A1" s="42" t="s">
         <v>251</v>
       </c>
@@ -3788,7 +4635,7 @@
       <c r="D1" s="43"/>
       <c r="E1" s="43"/>
     </row>
-    <row r="2" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:5" ht="16">
       <c r="A2" s="1" t="s">
         <v>0</v>
       </c>
@@ -3805,7 +4652,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:5" ht="16">
       <c r="A3" s="1" t="s">
         <v>9</v>
       </c>
@@ -3822,7 +4669,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:5" ht="16">
       <c r="A4" s="1" t="s">
         <v>12</v>
       </c>
@@ -3831,7 +4678,7 @@
       <c r="D4" s="2"/>
       <c r="E4" s="2"/>
     </row>
-    <row r="5" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:5" ht="16">
       <c r="A5" s="1" t="s">
         <v>14</v>
       </c>
@@ -3848,7 +4695,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:5" ht="16">
       <c r="A6" s="1" t="s">
         <v>15</v>
       </c>
@@ -3865,7 +4712,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:5">
       <c r="A7" s="39" t="s">
         <v>17</v>
       </c>
@@ -3882,7 +4729,7 @@
         <v>238</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:5">
       <c r="A8" s="39" t="s">
         <v>17</v>
       </c>
@@ -3899,7 +4746,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:5">
       <c r="A9" s="39" t="s">
         <v>17</v>
       </c>
@@ -3917,7 +4764,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:5">
       <c r="A10" s="39" t="s">
         <v>17</v>
       </c>
@@ -3948,26 +4795,26 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:X17"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="17.125" style="9" customWidth="1"/>
-    <col min="2" max="2" width="17.875" style="9" customWidth="1"/>
-    <col min="3" max="4" width="15.125" style="9" customWidth="1"/>
-    <col min="5" max="5" width="26.875" style="9" customWidth="1"/>
-    <col min="6" max="6" width="19.75" style="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.125" style="9" customWidth="1"/>
-    <col min="8" max="8" width="23.125" style="9" customWidth="1"/>
+    <col min="1" max="1" width="17.1640625" style="9" customWidth="1"/>
+    <col min="2" max="2" width="17.83203125" style="9" customWidth="1"/>
+    <col min="3" max="4" width="15.1640625" style="9" customWidth="1"/>
+    <col min="5" max="5" width="26.83203125" style="9" customWidth="1"/>
+    <col min="6" max="6" width="19.6640625" style="9" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.1640625" style="9" customWidth="1"/>
+    <col min="8" max="8" width="23.1640625" style="9" customWidth="1"/>
     <col min="9" max="9" width="5" style="9" customWidth="1"/>
-    <col min="10" max="10" width="46.125" style="9" customWidth="1"/>
+    <col min="10" max="10" width="46.1640625" style="9" customWidth="1"/>
     <col min="11" max="11" width="31.5" style="9" customWidth="1"/>
     <col min="12" max="12" width="8" style="9" customWidth="1"/>
-    <col min="13" max="13" width="73.625" style="9" customWidth="1"/>
-    <col min="14" max="14" width="13.125" style="9" customWidth="1"/>
-    <col min="15" max="15" width="20.625" style="8" customWidth="1"/>
+    <col min="13" max="13" width="73.6640625" style="9" customWidth="1"/>
+    <col min="14" max="14" width="13.1640625" style="9" customWidth="1"/>
+    <col min="15" max="15" width="20.6640625" style="8" customWidth="1"/>
     <col min="16" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:24">
       <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
@@ -4041,7 +4888,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:24">
       <c r="A2" s="21" t="s">
         <v>22</v>
       </c>
@@ -4115,7 +4962,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:24">
       <c r="A3" s="21" t="s">
         <v>12</v>
       </c>
@@ -4171,7 +5018,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:24">
       <c r="A4" s="21" t="s">
         <v>14</v>
       </c>
@@ -4245,7 +5092,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:24">
       <c r="A5" s="21" t="s">
         <v>15</v>
       </c>
@@ -4317,7 +5164,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:24" ht="17">
       <c r="A6" s="22">
         <v>1001</v>
       </c>
@@ -4384,7 +5231,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:24">
       <c r="A7" s="22">
         <v>1002</v>
       </c>
@@ -4444,7 +5291,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:24" ht="17">
       <c r="A8" s="22">
         <v>1003</v>
       </c>
@@ -4509,7 +5356,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:24" ht="17">
       <c r="A9" s="22">
         <v>1014</v>
       </c>
@@ -4571,7 +5418,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:24">
       <c r="A10" s="22">
         <v>100301</v>
       </c>
@@ -4641,7 +5488,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:24" ht="17">
       <c r="A11" s="22">
         <v>100302</v>
       </c>
@@ -4701,7 +5548,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="20" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:24" s="20" customFormat="1" ht="17">
       <c r="A12" s="24">
         <v>100303</v>
       </c>
@@ -4761,7 +5608,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:24" ht="17">
       <c r="A13" s="22">
         <v>100001</v>
       </c>
@@ -4821,7 +5668,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:24">
       <c r="A14" s="22">
         <v>100002</v>
       </c>
@@ -4881,7 +5728,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:24">
       <c r="A15" s="22">
         <v>100003</v>
       </c>
@@ -4943,7 +5790,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:24" ht="17">
       <c r="A16" s="22">
         <v>100304</v>
       </c>
@@ -5003,7 +5850,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:23" ht="17">
       <c r="A17" s="22">
         <v>1013</v>
       </c>
@@ -5075,27 +5922,27 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:X16"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="1" width="17.125" style="9" customWidth="1"/>
-    <col min="2" max="3" width="17.875" style="9" customWidth="1"/>
-    <col min="4" max="5" width="15.125" style="9" customWidth="1"/>
-    <col min="6" max="6" width="19.875" style="9" customWidth="1"/>
+    <col min="1" max="1" width="17.1640625" style="9" customWidth="1"/>
+    <col min="2" max="3" width="17.83203125" style="9" customWidth="1"/>
+    <col min="4" max="5" width="15.1640625" style="9" customWidth="1"/>
+    <col min="6" max="6" width="19.83203125" style="9" customWidth="1"/>
     <col min="7" max="7" width="28" style="9" customWidth="1"/>
-    <col min="8" max="8" width="15.125" style="9" customWidth="1"/>
-    <col min="9" max="9" width="23.125" style="9" customWidth="1"/>
-    <col min="10" max="10" width="16.125" style="9" customWidth="1"/>
-    <col min="11" max="11" width="63.125" style="9" customWidth="1"/>
-    <col min="12" max="12" width="8.875" style="9" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="20.125" style="9" customWidth="1"/>
-    <col min="14" max="14" width="13.125" style="9" customWidth="1"/>
+    <col min="8" max="8" width="15.1640625" style="9" customWidth="1"/>
+    <col min="9" max="9" width="23.1640625" style="9" customWidth="1"/>
+    <col min="10" max="10" width="16.1640625" style="9" customWidth="1"/>
+    <col min="11" max="11" width="63.1640625" style="9" customWidth="1"/>
+    <col min="12" max="12" width="8.83203125" style="9" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="20.1640625" style="9" customWidth="1"/>
+    <col min="14" max="14" width="13.1640625" style="9" customWidth="1"/>
     <col min="15" max="15" width="9" style="9"/>
-    <col min="16" max="16" width="13.125" style="9" customWidth="1"/>
+    <col min="16" max="16" width="13.1640625" style="9" customWidth="1"/>
     <col min="17" max="17" width="11" style="9" customWidth="1"/>
     <col min="18" max="16384" width="9" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:24">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -5166,7 +6013,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="2" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:24">
       <c r="A2" s="1" t="s">
         <v>22</v>
       </c>
@@ -5237,7 +6084,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:24">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -5289,7 +6136,7 @@
       </c>
       <c r="X3" s="1"/>
     </row>
-    <row r="4" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:24">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -5361,7 +6208,7 @@
       </c>
       <c r="X4" s="12"/>
     </row>
-    <row r="5" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:24">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
@@ -5430,7 +6277,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="6" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:24">
       <c r="A6" s="9">
         <f t="shared" ref="A6:A16" si="0">200000+C6*100+D6</f>
         <v>200101</v>
@@ -5490,7 +6337,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:24">
       <c r="A7" s="9">
         <f t="shared" si="0"/>
         <v>200102</v>
@@ -5549,7 +6396,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:24">
       <c r="A8" s="9">
         <f t="shared" si="0"/>
         <v>200103</v>
@@ -5611,7 +6458,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:24">
       <c r="A9" s="9">
         <f t="shared" si="0"/>
         <v>200104</v>
@@ -5670,7 +6517,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:24">
       <c r="A10" s="9">
         <f t="shared" si="0"/>
         <v>200105</v>
@@ -5729,7 +6576,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:24">
       <c r="A11" s="9">
         <f t="shared" si="0"/>
         <v>200106</v>
@@ -5788,7 +6635,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:24">
       <c r="A12" s="9">
         <f t="shared" si="0"/>
         <v>200107</v>
@@ -5847,7 +6694,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:24">
       <c r="A13" s="9">
         <f t="shared" si="0"/>
         <v>200201</v>
@@ -5909,7 +6756,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:24">
       <c r="A14" s="9">
         <f t="shared" si="0"/>
         <v>200202</v>
@@ -5971,7 +6818,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:24">
       <c r="A15" s="9">
         <f t="shared" si="0"/>
         <v>200203</v>
@@ -6033,7 +6880,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:24" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:24">
       <c r="A16" s="9">
         <f t="shared" si="0"/>
         <v>200204</v>
@@ -6101,21 +6948,22 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <sheetPr>
     <tabColor theme="5" tint="0.39915158543656726"/>
   </sheetPr>
-  <dimension ref="A1:I19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:J19"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="2" width="17.125" customWidth="1"/>
-    <col min="3" max="3" width="15.125" style="9" customWidth="1"/>
-    <col min="4" max="7" width="17.125" customWidth="1"/>
-    <col min="8" max="8" width="20.125" customWidth="1"/>
-    <col min="9" max="9" width="13.125" style="9" customWidth="1"/>
+    <col min="1" max="2" width="17.1640625" customWidth="1"/>
+    <col min="3" max="3" width="15.1640625" style="9" customWidth="1"/>
+    <col min="4" max="7" width="17.1640625" customWidth="1"/>
+    <col min="8" max="8" width="20.1640625" customWidth="1"/>
+    <col min="9" max="9" width="13.1640625" style="9" customWidth="1"/>
+    <col min="10" max="10" width="39.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6143,8 +6991,11 @@
       <c r="I1" s="2" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J1" s="2" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" s="1" t="s">
         <v>22</v>
       </c>
@@ -6172,8 +7023,11 @@
       <c r="I2" s="2" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J2" s="2" t="s">
+        <v>273</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -6193,8 +7047,9 @@
       <c r="I3" s="2" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J3" s="2"/>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -6222,8 +7077,11 @@
       <c r="I4" s="2" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J4" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
@@ -6251,8 +7109,11 @@
       <c r="I5" s="7" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J5" s="13" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" s="4" t="s">
         <v>175</v>
       </c>
@@ -6280,8 +7141,11 @@
       <c r="I6" s="6">
         <v>0</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J6" s="19" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" s="4" t="s">
         <v>181</v>
       </c>
@@ -6309,8 +7173,11 @@
       <c r="I7" s="6">
         <v>0</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="J7" s="8" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8" s="4" t="s">
         <v>186</v>
       </c>
@@ -6339,7 +7206,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10">
       <c r="A9" s="4" t="s">
         <v>191</v>
       </c>
@@ -6368,7 +7235,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10">
       <c r="A10" s="4"/>
       <c r="B10" s="5"/>
       <c r="C10" s="6"/>
@@ -6379,7 +7246,7 @@
       <c r="H10" s="6"/>
       <c r="I10" s="6"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10">
       <c r="A11" s="4"/>
       <c r="B11" s="5"/>
       <c r="C11" s="6"/>
@@ -6390,7 +7257,7 @@
       <c r="H11" s="6"/>
       <c r="I11" s="6"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10">
       <c r="A12" s="4"/>
       <c r="B12" s="5"/>
       <c r="C12" s="6"/>
@@ -6401,7 +7268,7 @@
       <c r="H12" s="6"/>
       <c r="I12" s="6"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10">
       <c r="A13" s="4"/>
       <c r="B13" s="5"/>
       <c r="C13" s="6"/>
@@ -6412,7 +7279,7 @@
       <c r="H13" s="6"/>
       <c r="I13" s="6"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10">
       <c r="A14" s="4"/>
       <c r="B14" s="5"/>
       <c r="C14" s="6"/>
@@ -6423,7 +7290,7 @@
       <c r="H14" s="6"/>
       <c r="I14" s="6"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10">
       <c r="A15" s="4"/>
       <c r="B15" s="5"/>
       <c r="C15" s="6"/>
@@ -6434,7 +7301,7 @@
       <c r="H15" s="6"/>
       <c r="I15" s="6"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10">
       <c r="A16" s="4"/>
       <c r="B16" s="5"/>
       <c r="C16" s="6"/>
@@ -6445,7 +7312,7 @@
       <c r="H16" s="6"/>
       <c r="I16" s="6"/>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:9">
       <c r="A17" s="4"/>
       <c r="B17" s="5"/>
       <c r="C17" s="6"/>
@@ -6456,7 +7323,7 @@
       <c r="H17" s="6"/>
       <c r="I17" s="6"/>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:9">
       <c r="A18" s="4"/>
       <c r="B18" s="5"/>
       <c r="C18" s="6"/>
@@ -6467,7 +7334,7 @@
       <c r="H18" s="6"/>
       <c r="I18" s="6"/>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:9">
       <c r="A19" s="4"/>
       <c r="B19" s="5"/>
       <c r="C19" s="6"/>
@@ -6482,6 +7349,7 @@
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6491,17 +7359,17 @@
     <tabColor theme="5" tint="0.39915158543656726"/>
   </sheetPr>
   <dimension ref="A1:J19"/>
-  <sheetFormatPr defaultColWidth="17.125" defaultRowHeight="16.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="17.1640625" defaultRowHeight="16"/>
   <cols>
-    <col min="1" max="2" width="17.125" customWidth="1"/>
-    <col min="3" max="3" width="15.125" style="9" customWidth="1"/>
-    <col min="4" max="7" width="17.125" customWidth="1"/>
-    <col min="8" max="9" width="25.625" customWidth="1"/>
-    <col min="10" max="10" width="13.125" style="9" customWidth="1"/>
-    <col min="11" max="16377" width="17.125" customWidth="1"/>
+    <col min="1" max="2" width="17.1640625" customWidth="1"/>
+    <col min="3" max="3" width="15.1640625" style="9" customWidth="1"/>
+    <col min="4" max="7" width="17.1640625" customWidth="1"/>
+    <col min="8" max="9" width="25.6640625" customWidth="1"/>
+    <col min="10" max="10" width="13.1640625" style="9" customWidth="1"/>
+    <col min="11" max="16377" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="16.5">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6533,7 +7401,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" ht="16.5">
       <c r="A2" s="1" t="s">
         <v>22</v>
       </c>
@@ -6565,7 +7433,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" ht="16.5">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -6587,7 +7455,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" ht="16.5">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -6619,7 +7487,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" ht="16.5">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
@@ -6651,7 +7519,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10">
       <c r="A6" s="4" t="s">
         <v>198</v>
       </c>
@@ -6683,7 +7551,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10">
       <c r="A7" s="4" t="s">
         <v>200</v>
       </c>
@@ -6715,7 +7583,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10">
       <c r="A8" s="4" t="s">
         <v>204</v>
       </c>
@@ -6747,7 +7615,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10">
       <c r="A9" s="4" t="s">
         <v>208</v>
       </c>
@@ -6779,7 +7647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10">
       <c r="A10" s="4"/>
       <c r="B10" s="5"/>
       <c r="C10" s="6"/>
@@ -6791,7 +7659,7 @@
       <c r="I10" s="6"/>
       <c r="J10" s="6"/>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10">
       <c r="A11" s="4"/>
       <c r="B11" s="5"/>
       <c r="C11" s="6"/>
@@ -6803,7 +7671,7 @@
       <c r="I11" s="6"/>
       <c r="J11" s="6"/>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10">
       <c r="A12" s="4"/>
       <c r="B12" s="5"/>
       <c r="C12" s="6"/>
@@ -6815,7 +7683,7 @@
       <c r="I12" s="6"/>
       <c r="J12" s="6"/>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10">
       <c r="A13" s="4"/>
       <c r="B13" s="5"/>
       <c r="C13" s="6"/>
@@ -6827,7 +7695,7 @@
       <c r="I13" s="6"/>
       <c r="J13" s="6"/>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10">
       <c r="A14" s="4"/>
       <c r="B14" s="5"/>
       <c r="C14" s="6"/>
@@ -6839,19 +7707,19 @@
       <c r="I14" s="6"/>
       <c r="J14" s="6"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10">
       <c r="J15" s="6"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10">
       <c r="J16" s="6"/>
     </row>
-    <row r="17" spans="10:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="10:10">
       <c r="J17" s="6"/>
     </row>
-    <row r="18" spans="10:10" x14ac:dyDescent="0.35">
+    <row r="18" spans="10:10">
       <c r="J18" s="6"/>
     </row>
-    <row r="19" spans="10:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="10:10">
       <c r="J19" s="6"/>
     </row>
   </sheetData>
@@ -6864,18 +7732,18 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A1:L9"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="4" max="4" width="10.625" customWidth="1"/>
+    <col min="4" max="4" width="10.6640625" customWidth="1"/>
     <col min="5" max="5" width="29" customWidth="1"/>
-    <col min="6" max="6" width="20.875" customWidth="1"/>
-    <col min="7" max="7" width="16.625" customWidth="1"/>
-    <col min="9" max="9" width="35.625" customWidth="1"/>
-    <col min="10" max="10" width="21.875" customWidth="1"/>
+    <col min="6" max="6" width="20.83203125" customWidth="1"/>
+    <col min="7" max="7" width="16.6640625" customWidth="1"/>
+    <col min="9" max="9" width="35.6640625" customWidth="1"/>
+    <col min="10" max="10" width="21.83203125" customWidth="1"/>
     <col min="12" max="12" width="52" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:12" ht="16">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6913,7 +7781,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:12" ht="16">
       <c r="A2" s="1" t="s">
         <v>22</v>
       </c>
@@ -6951,7 +7819,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:12" ht="16">
       <c r="A3" s="1" t="s">
         <v>12</v>
       </c>
@@ -6975,7 +7843,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:12" ht="16">
       <c r="A4" s="1" t="s">
         <v>14</v>
       </c>
@@ -7013,7 +7881,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="16.5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:12" ht="16">
       <c r="A5" s="1" t="s">
         <v>15</v>
       </c>
@@ -7051,7 +7919,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:12" ht="16">
       <c r="A6" s="4" t="s">
         <v>213</v>
       </c>
@@ -7085,7 +7953,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:12" ht="16">
       <c r="A7" s="4" t="s">
         <v>219</v>
       </c>
@@ -7119,7 +7987,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:12" ht="16">
       <c r="A8" s="4" t="s">
         <v>224</v>
       </c>
@@ -7153,7 +8021,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="16.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:12" ht="16">
       <c r="A9" s="4" t="s">
         <v>229</v>
       </c>
